--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2022.xlsx
@@ -1966,7 +1966,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:48</t>
+    <t xml:space="preserve">2026-09-07 12:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2022.xlsx
@@ -1966,7 +1966,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:53</t>
+    <t xml:space="preserve">2026-09-08 10:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
